--- a/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
+++ b/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valtterimj/Downloads/Työ/Aalto/Hera/Pipeline/Asteroid-spectra/v3.0/datasets/ASPECT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valtterimj/Downloads/Työ/Aalto/Hera/Pipeline/main/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FF8B8C-E107-AA40-AC88-94A65BBBA36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46DC1AF-1C98-A941-8226-CEA15CFF3497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="660" windowWidth="16520" windowHeight="16040" activeTab="1" xr2:uid="{3B7B7263-57CE-4670-B472-5AB98268D44C}"/>
   </bookViews>
@@ -3240,7 +3240,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42333228-403B-7F4C-BA26-71F42800C60A}">
-  <dimension ref="A3:A43"/>
+  <dimension ref="A3:A42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
@@ -3369,67 +3369,62 @@
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>1225</v>
+      <c r="A31" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>41</v>
+      <c r="A36">
+        <v>1400</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>1400</v>
+      <c r="A37" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="A42">
         <v>1575</v>
       </c>
     </row>

--- a/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
+++ b/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valtterimj/Downloads/Työ/Aalto/Hera/Pipeline/main/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46DC1AF-1C98-A941-8226-CEA15CFF3497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B5C659-FA67-4848-951A-1100BC07C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="660" windowWidth="16520" windowHeight="16040" activeTab="1" xr2:uid="{3B7B7263-57CE-4670-B472-5AB98268D44C}"/>
   </bookViews>

--- a/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
+++ b/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/REF_MEAS_upd_wl.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valtterimj/Downloads/Työ/Aalto/Hera/Pipeline/main/ASPECT_calibration_pipeline/level_3/datasets/ASPECT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B5C659-FA67-4848-951A-1100BC07C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DFFDE9-5C94-3B44-8AB5-B091F6B26505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="660" windowWidth="16520" windowHeight="16040" activeTab="1" xr2:uid="{3B7B7263-57CE-4670-B472-5AB98268D44C}"/>
   </bookViews>
   <sheets>
     <sheet name="600W, 10000|2500, LO" sheetId="1" r:id="rId1"/>
-    <sheet name="ASPECT default wl" sheetId="11" r:id="rId2"/>
-    <sheet name="600W, 10000|2500, HO" sheetId="2" r:id="rId3"/>
-    <sheet name="400W, 10000|2500, LO" sheetId="3" r:id="rId4"/>
-    <sheet name="400W, 10000|2500, HO" sheetId="4" r:id="rId5"/>
-    <sheet name="200W, 10000|2500, LO" sheetId="5" r:id="rId6"/>
-    <sheet name="200W, 10000|2500, HO" sheetId="6" r:id="rId7"/>
-    <sheet name="600W, 7500|1875, LO" sheetId="7" r:id="rId8"/>
-    <sheet name="600W, 7500|1875, HO" sheetId="8" r:id="rId9"/>
-    <sheet name="600W, 5000|1250, LO" sheetId="9" r:id="rId10"/>
-    <sheet name="600W, 5000|1250, HO" sheetId="10" r:id="rId11"/>
+    <sheet name="ASPECT meteorite wl" sheetId="12" r:id="rId2"/>
+    <sheet name="ASPECT default wl" sheetId="11" r:id="rId3"/>
+    <sheet name="600W, 10000|2500, HO" sheetId="2" r:id="rId4"/>
+    <sheet name="400W, 10000|2500, LO" sheetId="3" r:id="rId5"/>
+    <sheet name="400W, 10000|2500, HO" sheetId="4" r:id="rId6"/>
+    <sheet name="200W, 10000|2500, LO" sheetId="5" r:id="rId7"/>
+    <sheet name="200W, 10000|2500, HO" sheetId="6" r:id="rId8"/>
+    <sheet name="600W, 7500|1875, LO" sheetId="7" r:id="rId9"/>
+    <sheet name="600W, 7500|1875, HO" sheetId="8" r:id="rId10"/>
+    <sheet name="600W, 5000|1250, LO" sheetId="9" r:id="rId11"/>
+    <sheet name="600W, 5000|1250, HO" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="47">
   <si>
     <t>NIR1</t>
   </si>
@@ -193,10 +194,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -222,8 +230,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1517,6 +1526,867 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2694D348-F552-4FCA-971C-0A5A9ADA03D8}">
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>0.32536313</v>
+      </c>
+      <c r="B6">
+        <v>0.21698323999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.28290503</v>
+      </c>
+      <c r="D6">
+        <v>0.28245809999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.12715083999999999</v>
+      </c>
+      <c r="H6">
+        <v>0.12983239999999999</v>
+      </c>
+      <c r="I6">
+        <v>0.14391060999999999</v>
+      </c>
+      <c r="J6">
+        <v>0.12670391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>0.32</v>
+      </c>
+      <c r="B7">
+        <v>0.20218579</v>
+      </c>
+      <c r="C7">
+        <v>0.29245902000000001</v>
+      </c>
+      <c r="D7">
+        <v>0.29595628000000002</v>
+      </c>
+      <c r="G7">
+        <v>0.13027322</v>
+      </c>
+      <c r="H7">
+        <v>0.12918033000000001</v>
+      </c>
+      <c r="I7">
+        <v>0.13923497000000001</v>
+      </c>
+      <c r="J7">
+        <v>0.14295082000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>0.33414254999999998</v>
+      </c>
+      <c r="B8">
+        <v>0.22657952000000001</v>
+      </c>
+      <c r="C8">
+        <v>0.30202303000000003</v>
+      </c>
+      <c r="D8">
+        <v>0.30127607000000001</v>
+      </c>
+      <c r="G8">
+        <v>0.13569871999999999</v>
+      </c>
+      <c r="H8">
+        <v>0.13793962000000001</v>
+      </c>
+      <c r="I8">
+        <v>0.14665422</v>
+      </c>
+      <c r="J8">
+        <v>0.13071895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>0.32148731000000003</v>
+      </c>
+      <c r="B9">
+        <v>0.20707901000000001</v>
+      </c>
+      <c r="C9">
+        <v>0.26228101999999998</v>
+      </c>
+      <c r="D9">
+        <v>0.27515194999999998</v>
+      </c>
+      <c r="G9">
+        <v>0.12613514000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.13614587</v>
+      </c>
+      <c r="I9">
+        <v>0.14730067999999999</v>
+      </c>
+      <c r="J9">
+        <v>0.13671791</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>0.28786177000000002</v>
+      </c>
+      <c r="B10">
+        <v>0.20630670000000001</v>
+      </c>
+      <c r="C10">
+        <v>0.26643629000000002</v>
+      </c>
+      <c r="D10">
+        <v>0.28198704000000002</v>
+      </c>
+      <c r="G10">
+        <v>0.13753779999999999</v>
+      </c>
+      <c r="H10">
+        <v>0.13788337000000001</v>
+      </c>
+      <c r="I10">
+        <v>0.13857451000000001</v>
+      </c>
+      <c r="J10">
+        <v>0.13062635</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>0.31228615999999998</v>
+      </c>
+      <c r="B11">
+        <v>0.2086055</v>
+      </c>
+      <c r="C11">
+        <v>0.27993779000000002</v>
+      </c>
+      <c r="D11">
+        <v>0.28325557000000001</v>
+      </c>
+      <c r="G11">
+        <v>0.12897875</v>
+      </c>
+      <c r="H11">
+        <v>0.13478486000000001</v>
+      </c>
+      <c r="I11">
+        <v>0.13727320000000001</v>
+      </c>
+      <c r="J11">
+        <v>0.13851737</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>0.30970816000000001</v>
+      </c>
+      <c r="B12">
+        <v>0.19916617</v>
+      </c>
+      <c r="C12">
+        <v>0.26730197</v>
+      </c>
+      <c r="D12">
+        <v>0.26015484999999999</v>
+      </c>
+      <c r="G12">
+        <v>0.12626562999999999</v>
+      </c>
+      <c r="H12">
+        <v>0.13317451</v>
+      </c>
+      <c r="I12">
+        <v>0.13317451</v>
+      </c>
+      <c r="J12">
+        <v>0.12078618000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>0.26941416000000001</v>
+      </c>
+      <c r="B15">
+        <v>0.22331376999999999</v>
+      </c>
+      <c r="C15">
+        <v>0.23663592</v>
+      </c>
+      <c r="D15">
+        <v>0.24181142999999999</v>
+      </c>
+      <c r="G15">
+        <v>0.1307296</v>
+      </c>
+      <c r="H15">
+        <v>0.14165568000000001</v>
+      </c>
+      <c r="I15">
+        <v>0.12536241000000001</v>
+      </c>
+      <c r="J15">
+        <v>0.13609679999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>0.26427701999999997</v>
+      </c>
+      <c r="B16">
+        <v>0.21940480000000001</v>
+      </c>
+      <c r="C16">
+        <v>0.23330013999999999</v>
+      </c>
+      <c r="D16">
+        <v>0.24091161</v>
+      </c>
+      <c r="G16">
+        <v>0.13125345999999999</v>
+      </c>
+      <c r="H16">
+        <v>0.13709481000000001</v>
+      </c>
+      <c r="I16">
+        <v>0.12390751</v>
+      </c>
+      <c r="J16">
+        <v>0.13859940000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0.25780839</v>
+      </c>
+      <c r="B17">
+        <v>0.21737898</v>
+      </c>
+      <c r="C17">
+        <v>0.22604821</v>
+      </c>
+      <c r="D17">
+        <v>0.23585173000000001</v>
+      </c>
+      <c r="G17">
+        <v>0.12898520999999999</v>
+      </c>
+      <c r="H17">
+        <v>0.13587199</v>
+      </c>
+      <c r="I17">
+        <v>0.12493417</v>
+      </c>
+      <c r="J17">
+        <v>0.13481872</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>0.25999612</v>
+      </c>
+      <c r="B18">
+        <v>0.21485360000000001</v>
+      </c>
+      <c r="C18">
+        <v>0.22710878000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.23323637999999999</v>
+      </c>
+      <c r="G18">
+        <v>0.1331782</v>
+      </c>
+      <c r="H18">
+        <v>0.14000388</v>
+      </c>
+      <c r="I18">
+        <v>0.12472368</v>
+      </c>
+      <c r="J18">
+        <v>0.13674617</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0.26280896999999998</v>
+      </c>
+      <c r="B19">
+        <v>0.21758958</v>
+      </c>
+      <c r="C19">
+        <v>0.22801303000000001</v>
+      </c>
+      <c r="D19">
+        <v>0.23736347999999999</v>
+      </c>
+      <c r="G19">
+        <v>0.13404867000000001</v>
+      </c>
+      <c r="H19">
+        <v>0.14079326</v>
+      </c>
+      <c r="I19">
+        <v>0.12523471999999999</v>
+      </c>
+      <c r="J19">
+        <v>0.13381873999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0.26251424000000001</v>
+      </c>
+      <c r="B20">
+        <v>0.21724268999999999</v>
+      </c>
+      <c r="C20">
+        <v>0.23220661000000001</v>
+      </c>
+      <c r="D20">
+        <v>0.23965059</v>
+      </c>
+      <c r="G20">
+        <v>0.13816939</v>
+      </c>
+      <c r="H20">
+        <v>0.14606912</v>
+      </c>
+      <c r="I20">
+        <v>0.13057348999999999</v>
+      </c>
+      <c r="J20">
+        <v>0.13786555</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0.26935284999999998</v>
+      </c>
+      <c r="B21">
+        <v>0.2238145</v>
+      </c>
+      <c r="C21">
+        <v>0.24084386999999999</v>
+      </c>
+      <c r="D21">
+        <v>0.24722988000000001</v>
+      </c>
+      <c r="G21">
+        <v>0.14018816000000001</v>
+      </c>
+      <c r="H21">
+        <v>0.14725838999999999</v>
+      </c>
+      <c r="I21">
+        <v>0.13235769</v>
+      </c>
+      <c r="J21">
+        <v>0.14421743000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0.27371149</v>
+      </c>
+      <c r="B22">
+        <v>0.22841191999999999</v>
+      </c>
+      <c r="C22">
+        <v>0.24515999999999999</v>
+      </c>
+      <c r="D22">
+        <v>0.25377329999999998</v>
+      </c>
+      <c r="G22">
+        <v>0.14459177000000001</v>
+      </c>
+      <c r="H22">
+        <v>0.15097199</v>
+      </c>
+      <c r="I22">
+        <v>0.13677598999999999</v>
+      </c>
+      <c r="J22">
+        <v>0.1469046</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>0.28374426000000003</v>
+      </c>
+      <c r="B23">
+        <v>0.23686626</v>
+      </c>
+      <c r="C23">
+        <v>0.25138221999999999</v>
+      </c>
+      <c r="D23">
+        <v>0.26504430000000001</v>
+      </c>
+      <c r="G23">
+        <v>0.14891663999999999</v>
+      </c>
+      <c r="H23">
+        <v>0.15711389000000001</v>
+      </c>
+      <c r="I23">
+        <v>0.13841392</v>
+      </c>
+      <c r="J23">
+        <v>0.15036823999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>0.28625696</v>
+      </c>
+      <c r="B24">
+        <v>0.23927519</v>
+      </c>
+      <c r="C24">
+        <v>0.25525597999999999</v>
+      </c>
+      <c r="D24">
+        <v>0.26748171999999998</v>
+      </c>
+      <c r="G24">
+        <v>0.15002729000000001</v>
+      </c>
+      <c r="H24">
+        <v>0.15806134999999999</v>
+      </c>
+      <c r="I24">
+        <v>0.13989739000000001</v>
+      </c>
+      <c r="J24">
+        <v>0.15063857999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>0.28963435999999998</v>
+      </c>
+      <c r="B25">
+        <v>0.24143935</v>
+      </c>
+      <c r="C25">
+        <v>0.26121879999999997</v>
+      </c>
+      <c r="D25">
+        <v>0.27421938000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.15173534999999999</v>
+      </c>
+      <c r="H25">
+        <v>0.15925711000000001</v>
+      </c>
+      <c r="I25">
+        <v>0.14022055</v>
+      </c>
+      <c r="J25">
+        <v>0.15340685000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>0.28378829999999999</v>
+      </c>
+      <c r="B26">
+        <v>0.23877437000000001</v>
+      </c>
+      <c r="C26">
+        <v>0.25715876999999998</v>
+      </c>
+      <c r="D26">
+        <v>0.26718662999999998</v>
+      </c>
+      <c r="G26">
+        <v>0.15220056000000001</v>
+      </c>
+      <c r="H26">
+        <v>0.16066852000000001</v>
+      </c>
+      <c r="I26">
+        <v>0.14362116999999999</v>
+      </c>
+      <c r="J26">
+        <v>0.15777158999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>0.29376601000000002</v>
+      </c>
+      <c r="B29">
+        <v>0.25664673999999998</v>
+      </c>
+      <c r="C29">
+        <v>0.26370622999999999</v>
+      </c>
+      <c r="D29">
+        <v>0.27611728000000002</v>
+      </c>
+      <c r="G29">
+        <v>0.15713066000000001</v>
+      </c>
+      <c r="H29">
+        <v>0.16578423</v>
+      </c>
+      <c r="I29">
+        <v>0.14893254</v>
+      </c>
+      <c r="J29">
+        <v>0.15508113000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>0.29608540999999999</v>
+      </c>
+      <c r="B30">
+        <v>0.25292526999999998</v>
+      </c>
+      <c r="C30">
+        <v>0.26841281</v>
+      </c>
+      <c r="D30">
+        <v>0.28241992999999999</v>
+      </c>
+      <c r="G30">
+        <v>0.15533095999999999</v>
+      </c>
+      <c r="H30">
+        <v>0.16045551999999999</v>
+      </c>
+      <c r="I30">
+        <v>0.15248399000000001</v>
+      </c>
+      <c r="J30">
+        <v>0.15703914999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>0.29966200999999998</v>
+      </c>
+      <c r="B31">
+        <v>0.25698750999999997</v>
+      </c>
+      <c r="C31">
+        <v>0.27191770999999998</v>
+      </c>
+      <c r="D31">
+        <v>0.27991182999999997</v>
+      </c>
+      <c r="G31">
+        <v>0.15694342</v>
+      </c>
+      <c r="H31">
+        <v>0.16329170000000001</v>
+      </c>
+      <c r="I31">
+        <v>0.15212344</v>
+      </c>
+      <c r="J31">
+        <v>0.15870682999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>0.29755951000000003</v>
+      </c>
+      <c r="B32">
+        <v>0.25815005000000002</v>
+      </c>
+      <c r="C32">
+        <v>0.27044289999999999</v>
+      </c>
+      <c r="D32">
+        <v>0.28321784</v>
+      </c>
+      <c r="G32">
+        <v>0.15980717</v>
+      </c>
+      <c r="H32">
+        <v>0.16486893999999999</v>
+      </c>
+      <c r="I32">
+        <v>0.15354022000000001</v>
+      </c>
+      <c r="J32">
+        <v>0.16161494000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>0.31028917</v>
+      </c>
+      <c r="B33">
+        <v>0.26778749000000002</v>
+      </c>
+      <c r="C33">
+        <v>0.28083388999999997</v>
+      </c>
+      <c r="D33">
+        <v>0.28930732999999997</v>
+      </c>
+      <c r="G33">
+        <v>0.16072628999999999</v>
+      </c>
+      <c r="H33">
+        <v>0.16973773</v>
+      </c>
+      <c r="I33">
+        <v>0.16139878999999999</v>
+      </c>
+      <c r="J33">
+        <v>0.16207128000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>0.31152036</v>
+      </c>
+      <c r="B34">
+        <v>0.26699406999999997</v>
+      </c>
+      <c r="C34">
+        <v>0.27730714000000001</v>
+      </c>
+      <c r="D34">
+        <v>0.28942090999999998</v>
+      </c>
+      <c r="G34">
+        <v>0.16369961</v>
+      </c>
+      <c r="H34">
+        <v>0.17417638999999999</v>
+      </c>
+      <c r="I34">
+        <v>0.16337220999999999</v>
+      </c>
+      <c r="J34">
+        <v>0.16599141000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>0.31354417000000001</v>
+      </c>
+      <c r="B35">
+        <v>0.2763795</v>
+      </c>
+      <c r="C35">
+        <v>0.28841876</v>
+      </c>
+      <c r="D35">
+        <v>0.30028353000000002</v>
+      </c>
+      <c r="G35">
+        <v>0.17256270000000001</v>
+      </c>
+      <c r="H35">
+        <v>0.17605234</v>
+      </c>
+      <c r="I35">
+        <v>0.1638386</v>
+      </c>
+      <c r="J35">
+        <v>0.16610686999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>0.3225498</v>
+      </c>
+      <c r="B36">
+        <v>0.27219124</v>
+      </c>
+      <c r="C36">
+        <v>0.28733068</v>
+      </c>
+      <c r="D36">
+        <v>0.30183267000000003</v>
+      </c>
+      <c r="G36">
+        <v>0.16780876</v>
+      </c>
+      <c r="H36">
+        <v>0.17752988</v>
+      </c>
+      <c r="I36">
+        <v>0.16191235000000001</v>
+      </c>
+      <c r="J36">
+        <v>0.16175299000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>0.31862464000000001</v>
+      </c>
+      <c r="B37">
+        <v>0.27828079999999999</v>
+      </c>
+      <c r="C37">
+        <v>0.28943648999999999</v>
+      </c>
+      <c r="D37">
+        <v>0.30196752999999998</v>
+      </c>
+      <c r="G37">
+        <v>0.16320916999999999</v>
+      </c>
+      <c r="H37">
+        <v>0.17818529</v>
+      </c>
+      <c r="I37">
+        <v>0.15801336999999999</v>
+      </c>
+      <c r="J37">
+        <v>0.16382044000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>0.32795436</v>
+      </c>
+      <c r="B38">
+        <v>0.28850856000000002</v>
+      </c>
+      <c r="C38">
+        <v>0.30073349999999999</v>
+      </c>
+      <c r="D38">
+        <v>0.31850041000000001</v>
+      </c>
+      <c r="G38">
+        <v>0.16821516</v>
+      </c>
+      <c r="H38">
+        <v>0.1801141</v>
+      </c>
+      <c r="I38">
+        <v>0.16886715999999999</v>
+      </c>
+      <c r="J38">
+        <v>0.17000815</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>0.32333332999999997</v>
+      </c>
+      <c r="B39">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="C39">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="D39">
+        <v>0.30433333000000001</v>
+      </c>
+      <c r="G39">
+        <v>0.16633333</v>
+      </c>
+      <c r="H39">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0.16083333</v>
+      </c>
+      <c r="J39">
+        <v>0.16750000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>0.32615938999999999</v>
+      </c>
+      <c r="B40">
+        <v>0.28509679999999998</v>
+      </c>
+      <c r="C40">
+        <v>0.29788384000000001</v>
+      </c>
+      <c r="D40">
+        <v>0.30670869000000001</v>
+      </c>
+      <c r="G40">
+        <v>0.16767222000000001</v>
+      </c>
+      <c r="H40">
+        <v>0.17991895999999999</v>
+      </c>
+      <c r="I40">
+        <v>0.15686628</v>
+      </c>
+      <c r="J40">
+        <v>0.1710941</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2FAC0B-EE3B-42E4-A7E5-2FA82B54F342}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2377,7 +3247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2F580E-9841-4024-8794-350037C7121D}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3239,6 +4109,185 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE64EDE-924D-A845-9F8E-E5C2B5540823}">
+  <dimension ref="A3:A37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>681.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>712.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>743.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>806.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>837.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>868.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>880.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>911.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>942.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>973.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>1003.85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>1034.6199999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>1065.3900000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>1096.1600000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>1126.93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>1157.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>1188.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>1219.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>1230.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>1261.54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>1292.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>1323.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1353.85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1384.62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1415.39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>1446.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>1476.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1507.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>1538.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>1569.24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42333228-403B-7F4C-BA26-71F42800C60A}">
   <dimension ref="A3:A42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3433,7 +4482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5418AFA3-7BE2-40D6-B428-AEBC912691F4}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4288,7 +5337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32FF4068-F092-4FA3-899F-F95F2AA20693}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5143,7 +6192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32CD98FB-A331-48CA-AB8A-6C15D9AAF3D0}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5998,7 +7047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA542B6F-8910-4C27-A3B9-56233D36282B}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -6853,7 +7902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E33ECEDF-2720-4E23-99EF-4313233ABC9E}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7708,7 +8757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F56B74-9E62-4622-9A68-4FC8248BB2CE}">
   <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8567,865 +9616,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2694D348-F552-4FCA-971C-0A5A9ADA03D8}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>0.32536313</v>
-      </c>
-      <c r="B6">
-        <v>0.21698323999999999</v>
-      </c>
-      <c r="C6">
-        <v>0.28290503</v>
-      </c>
-      <c r="D6">
-        <v>0.28245809999999999</v>
-      </c>
-      <c r="G6">
-        <v>0.12715083999999999</v>
-      </c>
-      <c r="H6">
-        <v>0.12983239999999999</v>
-      </c>
-      <c r="I6">
-        <v>0.14391060999999999</v>
-      </c>
-      <c r="J6">
-        <v>0.12670391</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>0.32</v>
-      </c>
-      <c r="B7">
-        <v>0.20218579</v>
-      </c>
-      <c r="C7">
-        <v>0.29245902000000001</v>
-      </c>
-      <c r="D7">
-        <v>0.29595628000000002</v>
-      </c>
-      <c r="G7">
-        <v>0.13027322</v>
-      </c>
-      <c r="H7">
-        <v>0.12918033000000001</v>
-      </c>
-      <c r="I7">
-        <v>0.13923497000000001</v>
-      </c>
-      <c r="J7">
-        <v>0.14295082000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>0.33414254999999998</v>
-      </c>
-      <c r="B8">
-        <v>0.22657952000000001</v>
-      </c>
-      <c r="C8">
-        <v>0.30202303000000003</v>
-      </c>
-      <c r="D8">
-        <v>0.30127607000000001</v>
-      </c>
-      <c r="G8">
-        <v>0.13569871999999999</v>
-      </c>
-      <c r="H8">
-        <v>0.13793962000000001</v>
-      </c>
-      <c r="I8">
-        <v>0.14665422</v>
-      </c>
-      <c r="J8">
-        <v>0.13071895</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>0.32148731000000003</v>
-      </c>
-      <c r="B9">
-        <v>0.20707901000000001</v>
-      </c>
-      <c r="C9">
-        <v>0.26228101999999998</v>
-      </c>
-      <c r="D9">
-        <v>0.27515194999999998</v>
-      </c>
-      <c r="G9">
-        <v>0.12613514000000001</v>
-      </c>
-      <c r="H9">
-        <v>0.13614587</v>
-      </c>
-      <c r="I9">
-        <v>0.14730067999999999</v>
-      </c>
-      <c r="J9">
-        <v>0.13671791</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>0.28786177000000002</v>
-      </c>
-      <c r="B10">
-        <v>0.20630670000000001</v>
-      </c>
-      <c r="C10">
-        <v>0.26643629000000002</v>
-      </c>
-      <c r="D10">
-        <v>0.28198704000000002</v>
-      </c>
-      <c r="G10">
-        <v>0.13753779999999999</v>
-      </c>
-      <c r="H10">
-        <v>0.13788337000000001</v>
-      </c>
-      <c r="I10">
-        <v>0.13857451000000001</v>
-      </c>
-      <c r="J10">
-        <v>0.13062635</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>0.31228615999999998</v>
-      </c>
-      <c r="B11">
-        <v>0.2086055</v>
-      </c>
-      <c r="C11">
-        <v>0.27993779000000002</v>
-      </c>
-      <c r="D11">
-        <v>0.28325557000000001</v>
-      </c>
-      <c r="G11">
-        <v>0.12897875</v>
-      </c>
-      <c r="H11">
-        <v>0.13478486000000001</v>
-      </c>
-      <c r="I11">
-        <v>0.13727320000000001</v>
-      </c>
-      <c r="J11">
-        <v>0.13851737</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>0.30970816000000001</v>
-      </c>
-      <c r="B12">
-        <v>0.19916617</v>
-      </c>
-      <c r="C12">
-        <v>0.26730197</v>
-      </c>
-      <c r="D12">
-        <v>0.26015484999999999</v>
-      </c>
-      <c r="G12">
-        <v>0.12626562999999999</v>
-      </c>
-      <c r="H12">
-        <v>0.13317451</v>
-      </c>
-      <c r="I12">
-        <v>0.13317451</v>
-      </c>
-      <c r="J12">
-        <v>0.12078618000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>0.26941416000000001</v>
-      </c>
-      <c r="B15">
-        <v>0.22331376999999999</v>
-      </c>
-      <c r="C15">
-        <v>0.23663592</v>
-      </c>
-      <c r="D15">
-        <v>0.24181142999999999</v>
-      </c>
-      <c r="G15">
-        <v>0.1307296</v>
-      </c>
-      <c r="H15">
-        <v>0.14165568000000001</v>
-      </c>
-      <c r="I15">
-        <v>0.12536241000000001</v>
-      </c>
-      <c r="J15">
-        <v>0.13609679999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>0.26427701999999997</v>
-      </c>
-      <c r="B16">
-        <v>0.21940480000000001</v>
-      </c>
-      <c r="C16">
-        <v>0.23330013999999999</v>
-      </c>
-      <c r="D16">
-        <v>0.24091161</v>
-      </c>
-      <c r="G16">
-        <v>0.13125345999999999</v>
-      </c>
-      <c r="H16">
-        <v>0.13709481000000001</v>
-      </c>
-      <c r="I16">
-        <v>0.12390751</v>
-      </c>
-      <c r="J16">
-        <v>0.13859940000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>0.25780839</v>
-      </c>
-      <c r="B17">
-        <v>0.21737898</v>
-      </c>
-      <c r="C17">
-        <v>0.22604821</v>
-      </c>
-      <c r="D17">
-        <v>0.23585173000000001</v>
-      </c>
-      <c r="G17">
-        <v>0.12898520999999999</v>
-      </c>
-      <c r="H17">
-        <v>0.13587199</v>
-      </c>
-      <c r="I17">
-        <v>0.12493417</v>
-      </c>
-      <c r="J17">
-        <v>0.13481872</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>0.25999612</v>
-      </c>
-      <c r="B18">
-        <v>0.21485360000000001</v>
-      </c>
-      <c r="C18">
-        <v>0.22710878000000001</v>
-      </c>
-      <c r="D18">
-        <v>0.23323637999999999</v>
-      </c>
-      <c r="G18">
-        <v>0.1331782</v>
-      </c>
-      <c r="H18">
-        <v>0.14000388</v>
-      </c>
-      <c r="I18">
-        <v>0.12472368</v>
-      </c>
-      <c r="J18">
-        <v>0.13674617</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>0.26280896999999998</v>
-      </c>
-      <c r="B19">
-        <v>0.21758958</v>
-      </c>
-      <c r="C19">
-        <v>0.22801303000000001</v>
-      </c>
-      <c r="D19">
-        <v>0.23736347999999999</v>
-      </c>
-      <c r="G19">
-        <v>0.13404867000000001</v>
-      </c>
-      <c r="H19">
-        <v>0.14079326</v>
-      </c>
-      <c r="I19">
-        <v>0.12523471999999999</v>
-      </c>
-      <c r="J19">
-        <v>0.13381873999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>0.26251424000000001</v>
-      </c>
-      <c r="B20">
-        <v>0.21724268999999999</v>
-      </c>
-      <c r="C20">
-        <v>0.23220661000000001</v>
-      </c>
-      <c r="D20">
-        <v>0.23965059</v>
-      </c>
-      <c r="G20">
-        <v>0.13816939</v>
-      </c>
-      <c r="H20">
-        <v>0.14606912</v>
-      </c>
-      <c r="I20">
-        <v>0.13057348999999999</v>
-      </c>
-      <c r="J20">
-        <v>0.13786555</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>0.26935284999999998</v>
-      </c>
-      <c r="B21">
-        <v>0.2238145</v>
-      </c>
-      <c r="C21">
-        <v>0.24084386999999999</v>
-      </c>
-      <c r="D21">
-        <v>0.24722988000000001</v>
-      </c>
-      <c r="G21">
-        <v>0.14018816000000001</v>
-      </c>
-      <c r="H21">
-        <v>0.14725838999999999</v>
-      </c>
-      <c r="I21">
-        <v>0.13235769</v>
-      </c>
-      <c r="J21">
-        <v>0.14421743000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>0.27371149</v>
-      </c>
-      <c r="B22">
-        <v>0.22841191999999999</v>
-      </c>
-      <c r="C22">
-        <v>0.24515999999999999</v>
-      </c>
-      <c r="D22">
-        <v>0.25377329999999998</v>
-      </c>
-      <c r="G22">
-        <v>0.14459177000000001</v>
-      </c>
-      <c r="H22">
-        <v>0.15097199</v>
-      </c>
-      <c r="I22">
-        <v>0.13677598999999999</v>
-      </c>
-      <c r="J22">
-        <v>0.1469046</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>0.28374426000000003</v>
-      </c>
-      <c r="B23">
-        <v>0.23686626</v>
-      </c>
-      <c r="C23">
-        <v>0.25138221999999999</v>
-      </c>
-      <c r="D23">
-        <v>0.26504430000000001</v>
-      </c>
-      <c r="G23">
-        <v>0.14891663999999999</v>
-      </c>
-      <c r="H23">
-        <v>0.15711389000000001</v>
-      </c>
-      <c r="I23">
-        <v>0.13841392</v>
-      </c>
-      <c r="J23">
-        <v>0.15036823999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>0.28625696</v>
-      </c>
-      <c r="B24">
-        <v>0.23927519</v>
-      </c>
-      <c r="C24">
-        <v>0.25525597999999999</v>
-      </c>
-      <c r="D24">
-        <v>0.26748171999999998</v>
-      </c>
-      <c r="G24">
-        <v>0.15002729000000001</v>
-      </c>
-      <c r="H24">
-        <v>0.15806134999999999</v>
-      </c>
-      <c r="I24">
-        <v>0.13989739000000001</v>
-      </c>
-      <c r="J24">
-        <v>0.15063857999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>0.28963435999999998</v>
-      </c>
-      <c r="B25">
-        <v>0.24143935</v>
-      </c>
-      <c r="C25">
-        <v>0.26121879999999997</v>
-      </c>
-      <c r="D25">
-        <v>0.27421938000000001</v>
-      </c>
-      <c r="G25">
-        <v>0.15173534999999999</v>
-      </c>
-      <c r="H25">
-        <v>0.15925711000000001</v>
-      </c>
-      <c r="I25">
-        <v>0.14022055</v>
-      </c>
-      <c r="J25">
-        <v>0.15340685000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>0.28378829999999999</v>
-      </c>
-      <c r="B26">
-        <v>0.23877437000000001</v>
-      </c>
-      <c r="C26">
-        <v>0.25715876999999998</v>
-      </c>
-      <c r="D26">
-        <v>0.26718662999999998</v>
-      </c>
-      <c r="G26">
-        <v>0.15220056000000001</v>
-      </c>
-      <c r="H26">
-        <v>0.16066852000000001</v>
-      </c>
-      <c r="I26">
-        <v>0.14362116999999999</v>
-      </c>
-      <c r="J26">
-        <v>0.15777158999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>0.29376601000000002</v>
-      </c>
-      <c r="B29">
-        <v>0.25664673999999998</v>
-      </c>
-      <c r="C29">
-        <v>0.26370622999999999</v>
-      </c>
-      <c r="D29">
-        <v>0.27611728000000002</v>
-      </c>
-      <c r="G29">
-        <v>0.15713066000000001</v>
-      </c>
-      <c r="H29">
-        <v>0.16578423</v>
-      </c>
-      <c r="I29">
-        <v>0.14893254</v>
-      </c>
-      <c r="J29">
-        <v>0.15508113000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>0.29608540999999999</v>
-      </c>
-      <c r="B30">
-        <v>0.25292526999999998</v>
-      </c>
-      <c r="C30">
-        <v>0.26841281</v>
-      </c>
-      <c r="D30">
-        <v>0.28241992999999999</v>
-      </c>
-      <c r="G30">
-        <v>0.15533095999999999</v>
-      </c>
-      <c r="H30">
-        <v>0.16045551999999999</v>
-      </c>
-      <c r="I30">
-        <v>0.15248399000000001</v>
-      </c>
-      <c r="J30">
-        <v>0.15703914999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>0.29966200999999998</v>
-      </c>
-      <c r="B31">
-        <v>0.25698750999999997</v>
-      </c>
-      <c r="C31">
-        <v>0.27191770999999998</v>
-      </c>
-      <c r="D31">
-        <v>0.27991182999999997</v>
-      </c>
-      <c r="G31">
-        <v>0.15694342</v>
-      </c>
-      <c r="H31">
-        <v>0.16329170000000001</v>
-      </c>
-      <c r="I31">
-        <v>0.15212344</v>
-      </c>
-      <c r="J31">
-        <v>0.15870682999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>0.29755951000000003</v>
-      </c>
-      <c r="B32">
-        <v>0.25815005000000002</v>
-      </c>
-      <c r="C32">
-        <v>0.27044289999999999</v>
-      </c>
-      <c r="D32">
-        <v>0.28321784</v>
-      </c>
-      <c r="G32">
-        <v>0.15980717</v>
-      </c>
-      <c r="H32">
-        <v>0.16486893999999999</v>
-      </c>
-      <c r="I32">
-        <v>0.15354022000000001</v>
-      </c>
-      <c r="J32">
-        <v>0.16161494000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>0.31028917</v>
-      </c>
-      <c r="B33">
-        <v>0.26778749000000002</v>
-      </c>
-      <c r="C33">
-        <v>0.28083388999999997</v>
-      </c>
-      <c r="D33">
-        <v>0.28930732999999997</v>
-      </c>
-      <c r="G33">
-        <v>0.16072628999999999</v>
-      </c>
-      <c r="H33">
-        <v>0.16973773</v>
-      </c>
-      <c r="I33">
-        <v>0.16139878999999999</v>
-      </c>
-      <c r="J33">
-        <v>0.16207128000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>0.31152036</v>
-      </c>
-      <c r="B34">
-        <v>0.26699406999999997</v>
-      </c>
-      <c r="C34">
-        <v>0.27730714000000001</v>
-      </c>
-      <c r="D34">
-        <v>0.28942090999999998</v>
-      </c>
-      <c r="G34">
-        <v>0.16369961</v>
-      </c>
-      <c r="H34">
-        <v>0.17417638999999999</v>
-      </c>
-      <c r="I34">
-        <v>0.16337220999999999</v>
-      </c>
-      <c r="J34">
-        <v>0.16599141000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>0.31354417000000001</v>
-      </c>
-      <c r="B35">
-        <v>0.2763795</v>
-      </c>
-      <c r="C35">
-        <v>0.28841876</v>
-      </c>
-      <c r="D35">
-        <v>0.30028353000000002</v>
-      </c>
-      <c r="G35">
-        <v>0.17256270000000001</v>
-      </c>
-      <c r="H35">
-        <v>0.17605234</v>
-      </c>
-      <c r="I35">
-        <v>0.1638386</v>
-      </c>
-      <c r="J35">
-        <v>0.16610686999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>0.3225498</v>
-      </c>
-      <c r="B36">
-        <v>0.27219124</v>
-      </c>
-      <c r="C36">
-        <v>0.28733068</v>
-      </c>
-      <c r="D36">
-        <v>0.30183267000000003</v>
-      </c>
-      <c r="G36">
-        <v>0.16780876</v>
-      </c>
-      <c r="H36">
-        <v>0.17752988</v>
-      </c>
-      <c r="I36">
-        <v>0.16191235000000001</v>
-      </c>
-      <c r="J36">
-        <v>0.16175299000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>0.31862464000000001</v>
-      </c>
-      <c r="B37">
-        <v>0.27828079999999999</v>
-      </c>
-      <c r="C37">
-        <v>0.28943648999999999</v>
-      </c>
-      <c r="D37">
-        <v>0.30196752999999998</v>
-      </c>
-      <c r="G37">
-        <v>0.16320916999999999</v>
-      </c>
-      <c r="H37">
-        <v>0.17818529</v>
-      </c>
-      <c r="I37">
-        <v>0.15801336999999999</v>
-      </c>
-      <c r="J37">
-        <v>0.16382044000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>0.32795436</v>
-      </c>
-      <c r="B38">
-        <v>0.28850856000000002</v>
-      </c>
-      <c r="C38">
-        <v>0.30073349999999999</v>
-      </c>
-      <c r="D38">
-        <v>0.31850041000000001</v>
-      </c>
-      <c r="G38">
-        <v>0.16821516</v>
-      </c>
-      <c r="H38">
-        <v>0.1801141</v>
-      </c>
-      <c r="I38">
-        <v>0.16886715999999999</v>
-      </c>
-      <c r="J38">
-        <v>0.17000815</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>0.32333332999999997</v>
-      </c>
-      <c r="B39">
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="C39">
-        <v>0.30049999999999999</v>
-      </c>
-      <c r="D39">
-        <v>0.30433333000000001</v>
-      </c>
-      <c r="G39">
-        <v>0.16633333</v>
-      </c>
-      <c r="H39">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="I39">
-        <v>0.16083333</v>
-      </c>
-      <c r="J39">
-        <v>0.16750000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>0.32615938999999999</v>
-      </c>
-      <c r="B40">
-        <v>0.28509679999999998</v>
-      </c>
-      <c r="C40">
-        <v>0.29788384000000001</v>
-      </c>
-      <c r="D40">
-        <v>0.30670869000000001</v>
-      </c>
-      <c r="G40">
-        <v>0.16767222000000001</v>
-      </c>
-      <c r="H40">
-        <v>0.17991895999999999</v>
-      </c>
-      <c r="I40">
-        <v>0.15686628</v>
-      </c>
-      <c r="J40">
-        <v>0.1710941</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>